--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -445,6 +445,118 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Weighted total by candidate cause — the tall bars are where to look</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1F4E79"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'X-Y matrix'!$A$15:$A$36</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'X-Y matrix'!$H$15:$H$36</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="low"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="3"/>
+        <tickMarkSkip val="3"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1359,5 +1471,6 @@
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -157,7 +157,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -206,6 +206,11 @@
         <bgColor rgb="FF1F2937"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECFAEF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -241,7 +246,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -374,6 +379,12 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1055,29 +1066,29 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="23">
-      <c r="A15" s="40" t="inlineStr">
-        <is>
-          <t>Ticket closed before the billing adjustment posts</t>
-        </is>
-      </c>
-      <c r="B15" s="40" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
+        <is>
+          <t>Ticket closed before the adjustment posts</t>
+        </is>
+      </c>
+      <c r="B15" s="45" t="inlineStr">
         <is>
           <t>Process</t>
         </is>
       </c>
-      <c r="C15" s="40" t="n">
+      <c r="C15" s="45" t="n">
         <v>9</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="40" t="n">
+      <c r="E15" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="F15" s="40" t="n">
+      <c r="F15" s="45" t="n">
         <v>6</v>
       </c>
-      <c r="G15" s="40" t="n">
+      <c r="G15" s="45" t="n">
         <v>9</v>
       </c>
       <c r="H15" s="41">
@@ -1090,13 +1101,31 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="23">
-      <c r="A16" s="43" t="n"/>
-      <c r="B16" s="43" t="n"/>
-      <c r="C16" s="43" t="n"/>
-      <c r="D16" s="43" t="n"/>
-      <c r="E16" s="43" t="n"/>
-      <c r="F16" s="43" t="n"/>
-      <c r="G16" s="43" t="n"/>
+      <c r="A16" s="46" t="inlineStr">
+        <is>
+          <t>Contact reason mis-tagged at triage</t>
+        </is>
+      </c>
+      <c r="B16" s="46" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C16" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E16" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="F16" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="G16" s="46" t="n">
+        <v>6</v>
+      </c>
       <c r="H16" s="41">
         <f>IF(COUNT(C16:G16)=0,"",SUMPRODUCT(C16:G16,$C$11:$G$11))</f>
         <v/>
@@ -1107,13 +1136,31 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="23">
-      <c r="A17" s="43" t="n"/>
-      <c r="B17" s="43" t="n"/>
-      <c r="C17" s="43" t="n"/>
-      <c r="D17" s="43" t="n"/>
-      <c r="E17" s="43" t="n"/>
-      <c r="F17" s="43" t="n"/>
-      <c r="G17" s="43" t="n"/>
+      <c r="A17" s="46" t="inlineStr">
+        <is>
+          <t>Billing Ops sweep runs once a day</t>
+        </is>
+      </c>
+      <c r="B17" s="46" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C17" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="E17" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="F17" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="46" t="n">
+        <v>5</v>
+      </c>
       <c r="H17" s="41">
         <f>IF(COUNT(C17:G17)=0,"",SUMPRODUCT(C17:G17,$C$11:$G$11))</f>
         <v/>
@@ -1124,13 +1171,31 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="23">
-      <c r="A18" s="43" t="n"/>
-      <c r="B18" s="43" t="n"/>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="43" t="n"/>
-      <c r="E18" s="43" t="n"/>
-      <c r="F18" s="43" t="n"/>
-      <c r="G18" s="43" t="n"/>
+      <c r="A18" s="46" t="inlineStr">
+        <is>
+          <t>Evidence requirements not stated to Tier 1</t>
+        </is>
+      </c>
+      <c r="B18" s="46" t="inlineStr">
+        <is>
+          <t>Method</t>
+        </is>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="E18" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="F18" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" s="46" t="n">
+        <v>4</v>
+      </c>
       <c r="H18" s="41">
         <f>IF(COUNT(C18:G18)=0,"",SUMPRODUCT(C18:G18,$C$11:$G$11))</f>
         <v/>
@@ -1141,13 +1206,31 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="23">
-      <c r="A19" s="43" t="n"/>
-      <c r="B19" s="43" t="n"/>
-      <c r="C19" s="43" t="n"/>
-      <c r="D19" s="43" t="n"/>
-      <c r="E19" s="43" t="n"/>
-      <c r="F19" s="43" t="n"/>
-      <c r="G19" s="43" t="n"/>
+      <c r="A19" s="46" t="inlineStr">
+        <is>
+          <t>Nightly batch has no failure alerting</t>
+        </is>
+      </c>
+      <c r="B19" s="46" t="inlineStr">
+        <is>
+          <t>Machine</t>
+        </is>
+      </c>
+      <c r="C19" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="F19" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="G19" s="46" t="n">
+        <v>3</v>
+      </c>
       <c r="H19" s="41">
         <f>IF(COUNT(C19:G19)=0,"",SUMPRODUCT(C19:G19,$C$11:$G$11))</f>
         <v/>
@@ -1158,13 +1241,31 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="23">
-      <c r="A20" s="43" t="n"/>
-      <c r="B20" s="43" t="n"/>
-      <c r="C20" s="43" t="n"/>
-      <c r="D20" s="43" t="n"/>
-      <c r="E20" s="43" t="n"/>
-      <c r="F20" s="43" t="n"/>
-      <c r="G20" s="43" t="n"/>
+      <c r="A20" s="46" t="inlineStr">
+        <is>
+          <t>New-hire tenure under 90 days</t>
+        </is>
+      </c>
+      <c r="B20" s="46" t="inlineStr">
+        <is>
+          <t>People</t>
+        </is>
+      </c>
+      <c r="C20" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="46" t="n">
+        <v>7</v>
+      </c>
+      <c r="E20" s="46" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" s="46" t="n">
+        <v>8</v>
+      </c>
       <c r="H20" s="41">
         <f>IF(COUNT(C20:G20)=0,"",SUMPRODUCT(C20:G20,$C$11:$G$11))</f>
         <v/>
@@ -1175,13 +1276,31 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="23">
-      <c r="A21" s="43" t="n"/>
-      <c r="B21" s="43" t="n"/>
-      <c r="C21" s="43" t="n"/>
-      <c r="D21" s="43" t="n"/>
-      <c r="E21" s="43" t="n"/>
-      <c r="F21" s="43" t="n"/>
-      <c r="G21" s="43" t="n"/>
+      <c r="A21" s="46" t="inlineStr">
+        <is>
+          <t>Credit authority not enforced in the tool</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="inlineStr">
+        <is>
+          <t>Machine</t>
+        </is>
+      </c>
+      <c r="C21" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="G21" s="46" t="n">
+        <v>4</v>
+      </c>
       <c r="H21" s="41">
         <f>IF(COUNT(C21:G21)=0,"",SUMPRODUCT(C21:G21,$C$11:$G$11))</f>
         <v/>
@@ -1192,13 +1311,31 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="23">
-      <c r="A22" s="43" t="n"/>
-      <c r="B22" s="43" t="n"/>
-      <c r="C22" s="43" t="n"/>
-      <c r="D22" s="43" t="n"/>
-      <c r="E22" s="43" t="n"/>
-      <c r="F22" s="43" t="n"/>
-      <c r="G22" s="43" t="n"/>
+      <c r="A22" s="46" t="inlineStr">
+        <is>
+          <t>Auto-close at 96 hours with no reminder</t>
+        </is>
+      </c>
+      <c r="B22" s="46" t="inlineStr">
+        <is>
+          <t>Process</t>
+        </is>
+      </c>
+      <c r="C22" s="46" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="46" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="46" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="46" t="n">
+        <v>7</v>
+      </c>
       <c r="H22" s="41">
         <f>IF(COUNT(C22:G22)=0,"",SUMPRODUCT(C22:G22,$C$11:$G$11))</f>
         <v/>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -493,6 +493,7 @@
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
+          <invertIfNegative val="0"/>
           <cat>
             <numRef>
               <f>'X-Y matrix'!$A$15:$A$36</f>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -156,8 +156,12 @@
       <color rgb="FF0000FF"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -211,6 +215,11 @@
         <fgColor rgb="FFECFAEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F7FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -246,7 +255,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -386,6 +395,8 @@
     <xf numFmtId="0" fontId="18" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,6 +520,40 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Mean score</v>
+          </tx>
+          <spPr>
+            <a:ln w="18000">
+              <a:solidFill>
+                <a:srgbClr val="C0392B"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <val>
+            <numRef>
+              <f>'X-Y matrix'!$J$15:$J$36</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -538,6 +583,9 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -548,7 +596,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>11</col>
       <colOff>0</colOff>
       <row>13</row>
       <rowOff>0</rowOff>
@@ -884,7 +932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="22" min="1" max="1"/>
@@ -1065,6 +1113,11 @@
           <t>Rank</t>
         </is>
       </c>
+      <c r="J14" s="47" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="23">
       <c r="A15" s="45" t="inlineStr">
@@ -1100,6 +1153,10 @@
         <f>IF(H15="","",RANK(H15,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J15" s="48">
+        <f>IF(H15="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="23">
       <c r="A16" s="46" t="inlineStr">
@@ -1135,6 +1192,10 @@
         <f>IF(H16="","",RANK(H16,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J16" s="48">
+        <f>IF(H16="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="23">
       <c r="A17" s="46" t="inlineStr">
@@ -1170,6 +1231,10 @@
         <f>IF(H17="","",RANK(H17,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J17" s="48">
+        <f>IF(H17="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="23">
       <c r="A18" s="46" t="inlineStr">
@@ -1205,6 +1270,10 @@
         <f>IF(H18="","",RANK(H18,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J18" s="48">
+        <f>IF(H18="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="23">
       <c r="A19" s="46" t="inlineStr">
@@ -1240,6 +1309,10 @@
         <f>IF(H19="","",RANK(H19,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J19" s="48">
+        <f>IF(H19="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="23">
       <c r="A20" s="46" t="inlineStr">
@@ -1275,6 +1348,10 @@
         <f>IF(H20="","",RANK(H20,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J20" s="48">
+        <f>IF(H20="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="23">
       <c r="A21" s="46" t="inlineStr">
@@ -1310,6 +1387,10 @@
         <f>IF(H21="","",RANK(H21,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J21" s="48">
+        <f>IF(H21="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="23">
       <c r="A22" s="46" t="inlineStr">
@@ -1343,6 +1424,10 @@
       </c>
       <c r="I22" s="42">
         <f>IF(H22="","",RANK(H22,$H$15:$H$35))</f>
+        <v/>
+      </c>
+      <c r="J22" s="48">
+        <f>IF(H22="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
     </row>
@@ -1362,6 +1447,10 @@
         <f>IF(H23="","",RANK(H23,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J23" s="48">
+        <f>IF(H23="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="23">
       <c r="A24" s="43" t="n"/>
@@ -1379,6 +1468,10 @@
         <f>IF(H24="","",RANK(H24,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J24" s="48">
+        <f>IF(H24="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="23">
       <c r="A25" s="43" t="n"/>
@@ -1396,6 +1489,10 @@
         <f>IF(H25="","",RANK(H25,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J25" s="48">
+        <f>IF(H25="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="23">
       <c r="A26" s="43" t="n"/>
@@ -1413,6 +1510,10 @@
         <f>IF(H26="","",RANK(H26,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J26" s="48">
+        <f>IF(H26="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="23">
       <c r="A27" s="43" t="n"/>
@@ -1430,6 +1531,10 @@
         <f>IF(H27="","",RANK(H27,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J27" s="48">
+        <f>IF(H27="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="23">
       <c r="A28" s="43" t="n"/>
@@ -1447,6 +1552,10 @@
         <f>IF(H28="","",RANK(H28,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J28" s="48">
+        <f>IF(H28="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="23">
       <c r="A29" s="43" t="n"/>
@@ -1464,6 +1573,10 @@
         <f>IF(H29="","",RANK(H29,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J29" s="48">
+        <f>IF(H29="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="23">
       <c r="A30" s="43" t="n"/>
@@ -1481,6 +1594,10 @@
         <f>IF(H30="","",RANK(H30,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J30" s="48">
+        <f>IF(H30="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="23">
       <c r="A31" s="43" t="n"/>
@@ -1498,6 +1615,10 @@
         <f>IF(H31="","",RANK(H31,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J31" s="48">
+        <f>IF(H31="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="23">
       <c r="A32" s="43" t="n"/>
@@ -1515,6 +1636,10 @@
         <f>IF(H32="","",RANK(H32,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J32" s="48">
+        <f>IF(H32="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="23">
       <c r="A33" s="43" t="n"/>
@@ -1532,6 +1657,10 @@
         <f>IF(H33="","",RANK(H33,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J33" s="48">
+        <f>IF(H33="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="23">
       <c r="A34" s="43" t="n"/>
@@ -1549,6 +1678,10 @@
         <f>IF(H34="","",RANK(H34,$H$15:$H$35))</f>
         <v/>
       </c>
+      <c r="J34" s="48">
+        <f>IF(H34="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="23">
       <c r="A35" s="43" t="n"/>
@@ -1564,6 +1697,16 @@
       </c>
       <c r="I35" s="42">
         <f>IF(H35="","",RANK(H35,$H$15:$H$35))</f>
+        <v/>
+      </c>
+      <c r="J35" s="48">
+        <f>IF(H35="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="J36" s="48">
+        <f>IF(H36="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
     </row>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -160,6 +160,11 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -255,7 +260,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -397,6 +402,10 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -483,7 +492,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Weighted total by candidate cause — the tall bars are where to look</a:t>
+              <a:t>Weighted total by candidate cause — ranked, tallest first</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -507,12 +516,12 @@
           <invertIfNegative val="0"/>
           <cat>
             <numRef>
-              <f>'X-Y matrix'!$A$15:$A$36</f>
+              <f>'X-Y matrix'!$M$15:$M$36</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'X-Y matrix'!$H$15:$H$36</f>
+              <f>'X-Y matrix'!$N$15:$N$36</f>
             </numRef>
           </val>
         </ser>
@@ -546,7 +555,7 @@
           </marker>
           <val>
             <numRef>
-              <f>'X-Y matrix'!$J$15:$J$36</f>
+              <f>'X-Y matrix'!$O$15:$O$36</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -596,7 +605,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>11</col>
+      <col>16</col>
       <colOff>0</colOff>
       <row>13</row>
       <rowOff>0</rowOff>
@@ -932,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="22" min="1" max="1"/>
@@ -1118,6 +1127,31 @@
           <t>Mean</t>
         </is>
       </c>
+      <c r="K14" s="49" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="L14" s="47" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="M14" s="47" t="inlineStr">
+        <is>
+          <t>Candidate cause</t>
+        </is>
+      </c>
+      <c r="N14" s="47" t="inlineStr">
+        <is>
+          <t>Weighted total</t>
+        </is>
+      </c>
+      <c r="O14" s="47" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="23">
       <c r="A15" s="45" t="inlineStr">
@@ -1157,6 +1191,25 @@
         <f>IF(H15="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K15" s="50">
+        <f>IF(H15="","",RANK(H15,$H$15:$H$36,0)+COUNTIF($H$15:H15,H15)-1)</f>
+        <v/>
+      </c>
+      <c r="L15" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L15,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N15" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L15,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O15" s="48">
+        <f>IF(N15="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="16" ht="30" customHeight="1" s="23">
       <c r="A16" s="46" t="inlineStr">
@@ -1196,6 +1249,25 @@
         <f>IF(H16="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K16" s="50">
+        <f>IF(H16="","",RANK(H16,$H$15:$H$36,0)+COUNTIF($H$15:H16,H16)-1)</f>
+        <v/>
+      </c>
+      <c r="L16" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L16,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N16" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L16,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O16" s="48">
+        <f>IF(N16="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="23">
       <c r="A17" s="46" t="inlineStr">
@@ -1235,6 +1307,25 @@
         <f>IF(H17="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K17" s="50">
+        <f>IF(H17="","",RANK(H17,$H$15:$H$36,0)+COUNTIF($H$15:H17,H17)-1)</f>
+        <v/>
+      </c>
+      <c r="L17" s="51" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L17,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N17" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L17,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O17" s="48">
+        <f>IF(N17="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="18" ht="30" customHeight="1" s="23">
       <c r="A18" s="46" t="inlineStr">
@@ -1274,6 +1365,25 @@
         <f>IF(H18="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K18" s="50">
+        <f>IF(H18="","",RANK(H18,$H$15:$H$36,0)+COUNTIF($H$15:H18,H18)-1)</f>
+        <v/>
+      </c>
+      <c r="L18" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="M18" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L18,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N18" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L18,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O18" s="48">
+        <f>IF(N18="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="19" ht="30" customHeight="1" s="23">
       <c r="A19" s="46" t="inlineStr">
@@ -1313,6 +1423,25 @@
         <f>IF(H19="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K19" s="50">
+        <f>IF(H19="","",RANK(H19,$H$15:$H$36,0)+COUNTIF($H$15:H19,H19)-1)</f>
+        <v/>
+      </c>
+      <c r="L19" s="51" t="n">
+        <v>5</v>
+      </c>
+      <c r="M19" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L19,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N19" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L19,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O19" s="48">
+        <f>IF(N19="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="20" ht="30" customHeight="1" s="23">
       <c r="A20" s="46" t="inlineStr">
@@ -1352,6 +1481,25 @@
         <f>IF(H20="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K20" s="50">
+        <f>IF(H20="","",RANK(H20,$H$15:$H$36,0)+COUNTIF($H$15:H20,H20)-1)</f>
+        <v/>
+      </c>
+      <c r="L20" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L20,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N20" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L20,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O20" s="48">
+        <f>IF(N20="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="21" ht="30" customHeight="1" s="23">
       <c r="A21" s="46" t="inlineStr">
@@ -1391,6 +1539,25 @@
         <f>IF(H21="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K21" s="50">
+        <f>IF(H21="","",RANK(H21,$H$15:$H$36,0)+COUNTIF($H$15:H21,H21)-1)</f>
+        <v/>
+      </c>
+      <c r="L21" s="51" t="n">
+        <v>7</v>
+      </c>
+      <c r="M21" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L21,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N21" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L21,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O21" s="48">
+        <f>IF(N21="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="22" ht="30" customHeight="1" s="23">
       <c r="A22" s="46" t="inlineStr">
@@ -1428,6 +1595,25 @@
       </c>
       <c r="J22" s="48">
         <f>IF(H22="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
+      <c r="K22" s="50">
+        <f>IF(H22="","",RANK(H22,$H$15:$H$36,0)+COUNTIF($H$15:H22,H22)-1)</f>
+        <v/>
+      </c>
+      <c r="L22" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="M22" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L22,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N22" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L22,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O22" s="48">
+        <f>IF(N22="","",AVERAGE($N$15:$N$36))</f>
         <v/>
       </c>
     </row>
@@ -1451,6 +1637,25 @@
         <f>IF(H23="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K23" s="50">
+        <f>IF(H23="","",RANK(H23,$H$15:$H$36,0)+COUNTIF($H$15:H23,H23)-1)</f>
+        <v/>
+      </c>
+      <c r="L23" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="M23" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L23,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N23" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L23,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O23" s="48">
+        <f>IF(N23="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="24" ht="30" customHeight="1" s="23">
       <c r="A24" s="43" t="n"/>
@@ -1472,6 +1677,25 @@
         <f>IF(H24="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K24" s="50">
+        <f>IF(H24="","",RANK(H24,$H$15:$H$36,0)+COUNTIF($H$15:H24,H24)-1)</f>
+        <v/>
+      </c>
+      <c r="L24" s="51" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L24,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N24" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L24,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O24" s="48">
+        <f>IF(N24="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="25" ht="30" customHeight="1" s="23">
       <c r="A25" s="43" t="n"/>
@@ -1493,6 +1717,25 @@
         <f>IF(H25="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K25" s="50">
+        <f>IF(H25="","",RANK(H25,$H$15:$H$36,0)+COUNTIF($H$15:H25,H25)-1)</f>
+        <v/>
+      </c>
+      <c r="L25" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="M25" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L25,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N25" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L25,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O25" s="48">
+        <f>IF(N25="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="26" ht="30" customHeight="1" s="23">
       <c r="A26" s="43" t="n"/>
@@ -1514,6 +1757,25 @@
         <f>IF(H26="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K26" s="50">
+        <f>IF(H26="","",RANK(H26,$H$15:$H$36,0)+COUNTIF($H$15:H26,H26)-1)</f>
+        <v/>
+      </c>
+      <c r="L26" s="51" t="n">
+        <v>12</v>
+      </c>
+      <c r="M26" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L26,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N26" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L26,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O26" s="48">
+        <f>IF(N26="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="27" ht="30" customHeight="1" s="23">
       <c r="A27" s="43" t="n"/>
@@ -1535,6 +1797,25 @@
         <f>IF(H27="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K27" s="50">
+        <f>IF(H27="","",RANK(H27,$H$15:$H$36,0)+COUNTIF($H$15:H27,H27)-1)</f>
+        <v/>
+      </c>
+      <c r="L27" s="51" t="n">
+        <v>13</v>
+      </c>
+      <c r="M27" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L27,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N27" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L27,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O27" s="48">
+        <f>IF(N27="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="28" ht="30" customHeight="1" s="23">
       <c r="A28" s="43" t="n"/>
@@ -1556,6 +1837,25 @@
         <f>IF(H28="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K28" s="50">
+        <f>IF(H28="","",RANK(H28,$H$15:$H$36,0)+COUNTIF($H$15:H28,H28)-1)</f>
+        <v/>
+      </c>
+      <c r="L28" s="51" t="n">
+        <v>14</v>
+      </c>
+      <c r="M28" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L28,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N28" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L28,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O28" s="48">
+        <f>IF(N28="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="29" ht="30" customHeight="1" s="23">
       <c r="A29" s="43" t="n"/>
@@ -1577,6 +1877,25 @@
         <f>IF(H29="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K29" s="50">
+        <f>IF(H29="","",RANK(H29,$H$15:$H$36,0)+COUNTIF($H$15:H29,H29)-1)</f>
+        <v/>
+      </c>
+      <c r="L29" s="51" t="n">
+        <v>15</v>
+      </c>
+      <c r="M29" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L29,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N29" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L29,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O29" s="48">
+        <f>IF(N29="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="30" ht="30" customHeight="1" s="23">
       <c r="A30" s="43" t="n"/>
@@ -1598,6 +1917,25 @@
         <f>IF(H30="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K30" s="50">
+        <f>IF(H30="","",RANK(H30,$H$15:$H$36,0)+COUNTIF($H$15:H30,H30)-1)</f>
+        <v/>
+      </c>
+      <c r="L30" s="51" t="n">
+        <v>16</v>
+      </c>
+      <c r="M30" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L30,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N30" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L30,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O30" s="48">
+        <f>IF(N30="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="31" ht="30" customHeight="1" s="23">
       <c r="A31" s="43" t="n"/>
@@ -1619,6 +1957,25 @@
         <f>IF(H31="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K31" s="50">
+        <f>IF(H31="","",RANK(H31,$H$15:$H$36,0)+COUNTIF($H$15:H31,H31)-1)</f>
+        <v/>
+      </c>
+      <c r="L31" s="51" t="n">
+        <v>17</v>
+      </c>
+      <c r="M31" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L31,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N31" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L31,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O31" s="48">
+        <f>IF(N31="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="32" ht="30" customHeight="1" s="23">
       <c r="A32" s="43" t="n"/>
@@ -1640,6 +1997,25 @@
         <f>IF(H32="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K32" s="50">
+        <f>IF(H32="","",RANK(H32,$H$15:$H$36,0)+COUNTIF($H$15:H32,H32)-1)</f>
+        <v/>
+      </c>
+      <c r="L32" s="51" t="n">
+        <v>18</v>
+      </c>
+      <c r="M32" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L32,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N32" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L32,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O32" s="48">
+        <f>IF(N32="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="33" ht="30" customHeight="1" s="23">
       <c r="A33" s="43" t="n"/>
@@ -1661,6 +2037,25 @@
         <f>IF(H33="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K33" s="50">
+        <f>IF(H33="","",RANK(H33,$H$15:$H$36,0)+COUNTIF($H$15:H33,H33)-1)</f>
+        <v/>
+      </c>
+      <c r="L33" s="51" t="n">
+        <v>19</v>
+      </c>
+      <c r="M33" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L33,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N33" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L33,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O33" s="48">
+        <f>IF(N33="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="34" ht="30" customHeight="1" s="23">
       <c r="A34" s="43" t="n"/>
@@ -1682,6 +2077,25 @@
         <f>IF(H34="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K34" s="50">
+        <f>IF(H34="","",RANK(H34,$H$15:$H$36,0)+COUNTIF($H$15:H34,H34)-1)</f>
+        <v/>
+      </c>
+      <c r="L34" s="51" t="n">
+        <v>20</v>
+      </c>
+      <c r="M34" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L34,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N34" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L34,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O34" s="48">
+        <f>IF(N34="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="23">
       <c r="A35" s="43" t="n"/>
@@ -1703,10 +2117,48 @@
         <f>IF(H35="","",AVERAGE($H$15:$H$36))</f>
         <v/>
       </c>
+      <c r="K35" s="50">
+        <f>IF(H35="","",RANK(H35,$H$15:$H$36,0)+COUNTIF($H$15:H35,H35)-1)</f>
+        <v/>
+      </c>
+      <c r="L35" s="51" t="n">
+        <v>21</v>
+      </c>
+      <c r="M35" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L35,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N35" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L35,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O35" s="48">
+        <f>IF(N35="","",AVERAGE($N$15:$N$36))</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="J36" s="48">
         <f>IF(H36="","",AVERAGE($H$15:$H$36))</f>
+        <v/>
+      </c>
+      <c r="K36" s="50">
+        <f>IF(H36="","",RANK(H36,$H$15:$H$36,0)+COUNTIF($H$15:H36,H36)-1)</f>
+        <v/>
+      </c>
+      <c r="L36" s="51" t="n">
+        <v>22</v>
+      </c>
+      <c r="M36" s="52">
+        <f>IFERROR(INDEX($A$15:$A$36,MATCH(L36,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="N36" s="48">
+        <f>IFERROR(INDEX($H$15:$H$36,MATCH(L36,$K$15:$K$36,0)),"")</f>
+        <v/>
+      </c>
+      <c r="O36" s="48">
+        <f>IF(N36="","",AVERAGE($N$15:$N$36))</f>
         <v/>
       </c>
     </row>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -505,6 +505,9 @@
         <ser>
           <idx val="0"/>
           <order val="0"/>
+          <tx>
+            <v>Weighted total</v>
+          </tx>
           <spPr>
             <a:solidFill>
               <a:srgbClr val="1F4E79"/>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -492,7 +492,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Weighted total by candidate cause — ranked, tallest first</a:t>
+              <a:t>Weighted total by candidate cause — the top three are where you start</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -509,22 +509,129 @@
             <v>Weighted total</v>
           </tx>
           <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1F4E79"/>
-            </a:solidFill>
             <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="B45309"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="5"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="6"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="7"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="8"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="9"/>
+            <spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
           <cat>
             <numRef>
-              <f>'X-Y matrix'!$M$15:$M$36</f>
+              <f>'X-Y matrix'!$M$15:$M$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'X-Y matrix'!$N$15:$N$36</f>
+              <f>'X-Y matrix'!$N$15:$N$24</f>
             </numRef>
           </val>
         </ser>
@@ -532,44 +639,10 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <v>Mean score</v>
-          </tx>
-          <spPr>
-            <a:ln w="18000">
-              <a:solidFill>
-                <a:srgbClr val="C0392B"/>
-              </a:solidFill>
-              <a:prstDash val="dash"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <val>
-            <numRef>
-              <f>'X-Y matrix'!$O$15:$O$36</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
       <catAx>
         <axId val="10"/>
         <scaling>
-          <orientation val="minMax"/>
+          <orientation val="maxMin"/>
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
@@ -578,8 +651,8 @@
         <tickLblPos val="low"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="3"/>
-        <tickMarkSkip val="3"/>
+        <tickLblSkip val="1"/>
+        <tickMarkSkip val="1"/>
       </catAx>
       <valAx>
         <axId val="100"/>
@@ -595,9 +668,6 @@
         <crossAx val="10"/>
       </valAx>
     </plotArea>
-    <legend>
-      <legendPos val="b"/>
-    </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
@@ -613,7 +683,7 @@
       <row>13</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="6120000" cy="3960000"/>
+    <ext cx="6120000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -1150,11 +1220,7 @@
           <t>Weighted total</t>
         </is>
       </c>
-      <c r="O14" s="47" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
+      <c r="O14" s="47" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="23">
       <c r="A15" s="45" t="inlineStr">
@@ -1209,10 +1275,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L15,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O15" s="48">
-        <f>IF(N15="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O15" s="48" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1" s="23">
       <c r="A16" s="46" t="inlineStr">
@@ -1267,10 +1330,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L16,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O16" s="48">
-        <f>IF(N16="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O16" s="48" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1" s="23">
       <c r="A17" s="46" t="inlineStr">
@@ -1325,10 +1385,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L17,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O17" s="48">
-        <f>IF(N17="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O17" s="48" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1" s="23">
       <c r="A18" s="46" t="inlineStr">
@@ -1383,10 +1440,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L18,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O18" s="48">
-        <f>IF(N18="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O18" s="48" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1" s="23">
       <c r="A19" s="46" t="inlineStr">
@@ -1441,10 +1495,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L19,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O19" s="48">
-        <f>IF(N19="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O19" s="48" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1" s="23">
       <c r="A20" s="46" t="inlineStr">
@@ -1499,10 +1550,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L20,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O20" s="48">
-        <f>IF(N20="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O20" s="48" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1" s="23">
       <c r="A21" s="46" t="inlineStr">
@@ -1557,10 +1605,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L21,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O21" s="48">
-        <f>IF(N21="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O21" s="48" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1" s="23">
       <c r="A22" s="46" t="inlineStr">
@@ -1615,10 +1660,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L22,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O22" s="48">
-        <f>IF(N22="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O22" s="48" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1" s="23">
       <c r="A23" s="43" t="n"/>
@@ -1655,10 +1697,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L23,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O23" s="48">
-        <f>IF(N23="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O23" s="48" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1" s="23">
       <c r="A24" s="43" t="n"/>
@@ -1695,10 +1734,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L24,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O24" s="48">
-        <f>IF(N24="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O24" s="48" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1" s="23">
       <c r="A25" s="43" t="n"/>
@@ -1735,10 +1771,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L25,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O25" s="48">
-        <f>IF(N25="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O25" s="48" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1" s="23">
       <c r="A26" s="43" t="n"/>
@@ -1775,10 +1808,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L26,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O26" s="48">
-        <f>IF(N26="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O26" s="48" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1" s="23">
       <c r="A27" s="43" t="n"/>
@@ -1815,10 +1845,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L27,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O27" s="48">
-        <f>IF(N27="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O27" s="48" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1" s="23">
       <c r="A28" s="43" t="n"/>
@@ -1855,10 +1882,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L28,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O28" s="48">
-        <f>IF(N28="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O28" s="48" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1" s="23">
       <c r="A29" s="43" t="n"/>
@@ -1895,10 +1919,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L29,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O29" s="48">
-        <f>IF(N29="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O29" s="48" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1" s="23">
       <c r="A30" s="43" t="n"/>
@@ -1935,10 +1956,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L30,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O30" s="48">
-        <f>IF(N30="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O30" s="48" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1" s="23">
       <c r="A31" s="43" t="n"/>
@@ -1975,10 +1993,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L31,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O31" s="48">
-        <f>IF(N31="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O31" s="48" t="n"/>
     </row>
     <row r="32" ht="30" customHeight="1" s="23">
       <c r="A32" s="43" t="n"/>
@@ -2015,10 +2030,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L32,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O32" s="48">
-        <f>IF(N32="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O32" s="48" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1" s="23">
       <c r="A33" s="43" t="n"/>
@@ -2055,10 +2067,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L33,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O33" s="48">
-        <f>IF(N33="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O33" s="48" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1" s="23">
       <c r="A34" s="43" t="n"/>
@@ -2095,10 +2104,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L34,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O34" s="48">
-        <f>IF(N34="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O34" s="48" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1" s="23">
       <c r="A35" s="43" t="n"/>
@@ -2135,10 +2141,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L35,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O35" s="48">
-        <f>IF(N35="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O35" s="48" t="n"/>
     </row>
     <row r="36">
       <c r="J36" s="48">
@@ -2160,10 +2163,7 @@
         <f>IFERROR(INDEX($H$15:$H$36,MATCH(L36,$K$15:$K$36,0)),"")</f>
         <v/>
       </c>
-      <c r="O36" s="48">
-        <f>IF(N36="","",AVERAGE($N$15:$N$36))</f>
-        <v/>
-      </c>
+      <c r="O36" s="48" t="n"/>
     </row>
     <row r="37" ht="25.5" customHeight="1" s="23">
       <c r="A37" s="44" t="inlineStr">

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -1195,11 +1195,7 @@
           <t>Rank</t>
         </is>
       </c>
-      <c r="J14" s="47" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
+      <c r="J14" s="47" t="n"/>
       <c r="K14" s="49" t="inlineStr">
         <is>
           <t>rank</t>
@@ -1256,10 +1252,7 @@
         <f>IF(H15="","",RANK(H15,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J15" s="48">
-        <f>IF(H15="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J15" s="48" t="n"/>
       <c r="K15" s="50">
         <f>IF(H15="","",RANK(H15,$H$15:$H$36,0)+COUNTIF($H$15:H15,H15)-1)</f>
         <v/>
@@ -1311,10 +1304,7 @@
         <f>IF(H16="","",RANK(H16,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J16" s="48">
-        <f>IF(H16="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J16" s="48" t="n"/>
       <c r="K16" s="50">
         <f>IF(H16="","",RANK(H16,$H$15:$H$36,0)+COUNTIF($H$15:H16,H16)-1)</f>
         <v/>
@@ -1366,10 +1356,7 @@
         <f>IF(H17="","",RANK(H17,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J17" s="48">
-        <f>IF(H17="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J17" s="48" t="n"/>
       <c r="K17" s="50">
         <f>IF(H17="","",RANK(H17,$H$15:$H$36,0)+COUNTIF($H$15:H17,H17)-1)</f>
         <v/>
@@ -1421,10 +1408,7 @@
         <f>IF(H18="","",RANK(H18,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J18" s="48">
-        <f>IF(H18="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J18" s="48" t="n"/>
       <c r="K18" s="50">
         <f>IF(H18="","",RANK(H18,$H$15:$H$36,0)+COUNTIF($H$15:H18,H18)-1)</f>
         <v/>
@@ -1476,10 +1460,7 @@
         <f>IF(H19="","",RANK(H19,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J19" s="48">
-        <f>IF(H19="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J19" s="48" t="n"/>
       <c r="K19" s="50">
         <f>IF(H19="","",RANK(H19,$H$15:$H$36,0)+COUNTIF($H$15:H19,H19)-1)</f>
         <v/>
@@ -1531,10 +1512,7 @@
         <f>IF(H20="","",RANK(H20,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J20" s="48">
-        <f>IF(H20="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J20" s="48" t="n"/>
       <c r="K20" s="50">
         <f>IF(H20="","",RANK(H20,$H$15:$H$36,0)+COUNTIF($H$15:H20,H20)-1)</f>
         <v/>
@@ -1586,10 +1564,7 @@
         <f>IF(H21="","",RANK(H21,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J21" s="48">
-        <f>IF(H21="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J21" s="48" t="n"/>
       <c r="K21" s="50">
         <f>IF(H21="","",RANK(H21,$H$15:$H$36,0)+COUNTIF($H$15:H21,H21)-1)</f>
         <v/>
@@ -1641,10 +1616,7 @@
         <f>IF(H22="","",RANK(H22,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J22" s="48">
-        <f>IF(H22="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J22" s="48" t="n"/>
       <c r="K22" s="50">
         <f>IF(H22="","",RANK(H22,$H$15:$H$36,0)+COUNTIF($H$15:H22,H22)-1)</f>
         <v/>
@@ -1678,10 +1650,7 @@
         <f>IF(H23="","",RANK(H23,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J23" s="48">
-        <f>IF(H23="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J23" s="48" t="n"/>
       <c r="K23" s="50">
         <f>IF(H23="","",RANK(H23,$H$15:$H$36,0)+COUNTIF($H$15:H23,H23)-1)</f>
         <v/>
@@ -1715,10 +1684,7 @@
         <f>IF(H24="","",RANK(H24,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J24" s="48">
-        <f>IF(H24="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J24" s="48" t="n"/>
       <c r="K24" s="50">
         <f>IF(H24="","",RANK(H24,$H$15:$H$36,0)+COUNTIF($H$15:H24,H24)-1)</f>
         <v/>
@@ -1752,10 +1718,7 @@
         <f>IF(H25="","",RANK(H25,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J25" s="48">
-        <f>IF(H25="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J25" s="48" t="n"/>
       <c r="K25" s="50">
         <f>IF(H25="","",RANK(H25,$H$15:$H$36,0)+COUNTIF($H$15:H25,H25)-1)</f>
         <v/>
@@ -1789,10 +1752,7 @@
         <f>IF(H26="","",RANK(H26,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J26" s="48">
-        <f>IF(H26="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J26" s="48" t="n"/>
       <c r="K26" s="50">
         <f>IF(H26="","",RANK(H26,$H$15:$H$36,0)+COUNTIF($H$15:H26,H26)-1)</f>
         <v/>
@@ -1826,10 +1786,7 @@
         <f>IF(H27="","",RANK(H27,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J27" s="48">
-        <f>IF(H27="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J27" s="48" t="n"/>
       <c r="K27" s="50">
         <f>IF(H27="","",RANK(H27,$H$15:$H$36,0)+COUNTIF($H$15:H27,H27)-1)</f>
         <v/>
@@ -1863,10 +1820,7 @@
         <f>IF(H28="","",RANK(H28,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J28" s="48">
-        <f>IF(H28="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J28" s="48" t="n"/>
       <c r="K28" s="50">
         <f>IF(H28="","",RANK(H28,$H$15:$H$36,0)+COUNTIF($H$15:H28,H28)-1)</f>
         <v/>
@@ -1900,10 +1854,7 @@
         <f>IF(H29="","",RANK(H29,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J29" s="48">
-        <f>IF(H29="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J29" s="48" t="n"/>
       <c r="K29" s="50">
         <f>IF(H29="","",RANK(H29,$H$15:$H$36,0)+COUNTIF($H$15:H29,H29)-1)</f>
         <v/>
@@ -1937,10 +1888,7 @@
         <f>IF(H30="","",RANK(H30,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J30" s="48">
-        <f>IF(H30="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J30" s="48" t="n"/>
       <c r="K30" s="50">
         <f>IF(H30="","",RANK(H30,$H$15:$H$36,0)+COUNTIF($H$15:H30,H30)-1)</f>
         <v/>
@@ -1974,10 +1922,7 @@
         <f>IF(H31="","",RANK(H31,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J31" s="48">
-        <f>IF(H31="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J31" s="48" t="n"/>
       <c r="K31" s="50">
         <f>IF(H31="","",RANK(H31,$H$15:$H$36,0)+COUNTIF($H$15:H31,H31)-1)</f>
         <v/>
@@ -2011,10 +1956,7 @@
         <f>IF(H32="","",RANK(H32,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J32" s="48">
-        <f>IF(H32="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J32" s="48" t="n"/>
       <c r="K32" s="50">
         <f>IF(H32="","",RANK(H32,$H$15:$H$36,0)+COUNTIF($H$15:H32,H32)-1)</f>
         <v/>
@@ -2048,10 +1990,7 @@
         <f>IF(H33="","",RANK(H33,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J33" s="48">
-        <f>IF(H33="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J33" s="48" t="n"/>
       <c r="K33" s="50">
         <f>IF(H33="","",RANK(H33,$H$15:$H$36,0)+COUNTIF($H$15:H33,H33)-1)</f>
         <v/>
@@ -2085,10 +2024,7 @@
         <f>IF(H34="","",RANK(H34,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J34" s="48">
-        <f>IF(H34="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J34" s="48" t="n"/>
       <c r="K34" s="50">
         <f>IF(H34="","",RANK(H34,$H$15:$H$36,0)+COUNTIF($H$15:H34,H34)-1)</f>
         <v/>
@@ -2122,10 +2058,7 @@
         <f>IF(H35="","",RANK(H35,$H$15:$H$35))</f>
         <v/>
       </c>
-      <c r="J35" s="48">
-        <f>IF(H35="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J35" s="48" t="n"/>
       <c r="K35" s="50">
         <f>IF(H35="","",RANK(H35,$H$15:$H$36,0)+COUNTIF($H$15:H35,H35)-1)</f>
         <v/>
@@ -2144,10 +2077,7 @@
       <c r="O35" s="48" t="n"/>
     </row>
     <row r="36">
-      <c r="J36" s="48">
-        <f>IF(H36="","",AVERAGE($H$15:$H$36))</f>
-        <v/>
-      </c>
+      <c r="J36" s="48" t="n"/>
       <c r="K36" s="50">
         <f>IF(H36="","",RANK(H36,$H$15:$H$36,0)+COUNTIF($H$15:H36,H36)-1)</f>
         <v/>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -678,9 +678,9 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>16</col>
+      <col>15</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>2</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6120000" cy="3240000"/>
@@ -1038,6 +1038,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="19.5" customHeight="1" s="23">
       <c r="A4" s="31" t="inlineStr">
         <is>
@@ -1081,6 +1082,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="19.5" customHeight="1" s="23">
       <c r="A9" s="31" t="inlineStr">
         <is>
@@ -1142,6 +1144,7 @@
         <v>9</v>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="19.5" customHeight="1" s="23">
       <c r="A13" s="31" t="inlineStr">
         <is>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -166,7 +166,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -225,6 +225,11 @@
         <fgColor rgb="FFF2F7FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF9E3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -260,7 +265,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -406,6 +411,12 @@
     <xf numFmtId="1" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1073,12 +1084,12 @@
     <row r="7" ht="15" customHeight="1" s="23">
       <c r="A7" s="35" t="inlineStr">
         <is>
-          <t>Row 1 example</t>
+          <t>Green cells</t>
         </is>
       </c>
       <c r="B7" s="33" t="inlineStr">
         <is>
-          <t>A realistic worked example, so you can see the expected format. Delete or overwrite it.</t>
+          <t>A realistic worked example, so you can see the expected format and the sheet is not blank when you open it. Replace it with your own.</t>
         </is>
       </c>
     </row>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -265,7 +265,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -416,6 +416,9 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1156,10 +1159,10 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="19.5" customHeight="1" s="23">
-      <c r="A13" s="31" t="inlineStr">
-        <is>
-          <t>STEP 2 — SCORE EACH CAUSE AGAINST EACH CTQ:  9 = strong  ·  6 = moderate  ·  3 = weak  ·  1 = none</t>
+    <row r="13" ht="84" customHeight="1" s="23">
+      <c r="A13" s="55" t="inlineStr">
+        <is>
+          <t>STEP 2 — SCORE EACH CAUSE AGAINST EACH CTQ:  9 = strong  ·  6 = moderate  ·  3 = weak  ·  1 = none  ·  Key: Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through · Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
         </is>
       </c>
     </row>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -1159,10 +1159,14 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="84" customHeight="1" s="23">
+    <row r="13" ht="180" customHeight="1" s="23">
       <c r="A13" s="55" t="inlineStr">
         <is>
-          <t>STEP 2 — SCORE EACH CAUSE AGAINST EACH CTQ:  9 = strong  ·  6 = moderate  ·  3 = weak  ·  1 = none  ·  Key: Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through · Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+          <t>STEP 2 — SCORE EACH CAUSE AGAINST EACH CTQ:  9 = strong  ·  6 = moderate  ·  3 = weak  ·  1 = none  ·  Key:
+• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
+• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
         </is>
       </c>
     </row>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -165,6 +165,11 @@
       <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FF4B5563"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -265,7 +270,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -419,6 +424,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -692,7 +700,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>15</col>
+      <col>18</col>
       <colOff>0</colOff>
       <row>2</row>
       <rowOff>0</rowOff>
@@ -1028,7 +1036,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="40" customWidth="1" style="22" min="1" max="1"/>
@@ -1036,6 +1044,15 @@
     <col width="13" customWidth="1" style="22" min="3" max="7"/>
     <col width="15" customWidth="1" style="22" min="8" max="8"/>
     <col width="8" customWidth="1" style="22" min="9" max="9"/>
+    <col width="13" customWidth="1" style="23" min="17" max="17"/>
+    <col width="13" customWidth="1" style="23" min="18" max="18"/>
+    <col width="13" customWidth="1" style="23" min="19" max="19"/>
+    <col width="13" customWidth="1" style="23" min="20" max="20"/>
+    <col width="13" customWidth="1" style="23" min="21" max="21"/>
+    <col width="13" customWidth="1" style="23" min="22" max="22"/>
+    <col width="13" customWidth="1" style="23" min="23" max="23"/>
+    <col width="13" customWidth="1" style="23" min="24" max="24"/>
+    <col width="13" customWidth="1" style="23" min="25" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="25.5" customHeight="1" s="23">
@@ -1159,10 +1176,14 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="180" customHeight="1" s="23">
+    <row r="13" ht="348" customHeight="1" s="23">
       <c r="A13" s="55" t="inlineStr">
         <is>
           <t>STEP 2 — SCORE EACH CAUSE AGAINST EACH CTQ:  9 = strong  ·  6 = moderate  ·  3 = weak  ·  1 = none  ·  Key:
+• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
+• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
+• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
 • Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
 • Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
 • Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
@@ -2029,7 +2050,7 @@
       </c>
       <c r="O33" s="48" t="n"/>
     </row>
-    <row r="34" ht="30" customHeight="1" s="23">
+    <row r="34" ht="66" customHeight="1" s="23">
       <c r="A34" s="43" t="n"/>
       <c r="B34" s="43" t="n"/>
       <c r="C34" s="43" t="n"/>
@@ -2062,6 +2083,12 @@
         <v/>
       </c>
       <c r="O34" s="48" t="n"/>
+      <c r="Q34" s="56" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Bars are the weighted totals, so height already accounts for which CTQ matters most. Look for a clear step down after the top few. Where the top bars are level — 270 against 261 here — the ranking is inside anyone's scoring noise, and you should treat them as one set to investigate rather than an order to work through.
+SO:  Take the top three into the fishbone and the FMEA together, not the top one on its own. 270 against 261 will not survive re-scoring by a different group.</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="30" customHeight="1" s="23">
       <c r="A35" s="43" t="n"/>
@@ -2124,7 +2151,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
+    <mergeCell ref="Q34:Y34"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="B6:F6"/>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -1176,16 +1176,10 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="348" customHeight="1" s="23">
+    <row r="13" ht="96" customHeight="1" s="23">
       <c r="A13" s="55" t="inlineStr">
         <is>
           <t>STEP 2 — SCORE EACH CAUSE AGAINST EACH CTQ:  9 = strong  ·  6 = moderate  ·  3 = weak  ·  1 = none  ·  Key:
-• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
-• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
-• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that  ·  Key:
 • Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
 • Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
         </is>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -270,7 +270,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -426,6 +426,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1001,9 +1004,27 @@
     </row>
     <row r="17"/>
     <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
+    <row r="19" ht="26" customHeight="1" s="23">
+      <c r="A19" s="57" t="inlineStr">
+        <is>
+          <t>WHAT THE COLUMNS MEAN — the short version sits above each table; this is the same thing with the worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="52" customHeight="1" s="23">
+      <c r="A20" s="56" t="inlineStr">
+        <is>
+          <t>Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="39" customHeight="1" s="23">
+      <c r="A21" s="56" t="inlineStr">
+        <is>
+          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+        </is>
+      </c>
+    </row>
     <row r="22"/>
     <row r="23"/>
     <row r="24"/>
@@ -1024,6 +1045,11 @@
     <row r="39"/>
     <row r="40"/>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A19:B19"/>
+  </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1176,12 +1202,12 @@
       </c>
     </row>
     <row r="12"/>
-    <row r="13" ht="96" customHeight="1" s="23">
+    <row r="13" ht="36" customHeight="1" s="23">
       <c r="A13" s="55" t="inlineStr">
         <is>
           <t>STEP 2 — SCORE EACH CAUSE AGAINST EACH CTQ:  9 = strong  ·  6 = moderate  ·  3 = weak  ·  1 = none  ·  Key:
-• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through
-• Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+• Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up.
+• Rank = position by weighted total, 1 being highest.</t>
         </is>
       </c>
     </row>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -1046,8 +1046,8 @@
     <row r="40"/>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A20:B20"/>
     <mergeCell ref="A19:B19"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -270,7 +270,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -429,6 +429,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -912,6 +915,12 @@
   <cols>
     <col width="3" customWidth="1" style="22" min="1" max="1"/>
     <col width="108" customWidth="1" style="22" min="2" max="2"/>
+    <col width="13" customWidth="1" style="23" min="3" max="3"/>
+    <col width="13" customWidth="1" style="23" min="4" max="4"/>
+    <col width="13" customWidth="1" style="23" min="5" max="5"/>
+    <col width="13" customWidth="1" style="23" min="6" max="6"/>
+    <col width="13" customWidth="1" style="23" min="7" max="7"/>
+    <col width="13" customWidth="1" style="23" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -1011,17 +1020,17 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="52" customHeight="1" s="23">
+    <row r="20" ht="33" customHeight="1" s="23">
       <c r="A20" s="56" t="inlineStr">
         <is>
-          <t>Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 7, 8, 5 and 9 (C11:G11) the closing-before-posting row totals 270 (H15). It is a ranking device, not a measurement — the gap between 270 and 261 is inside anyone's scoring noise, so treat the top few as a set to investigate rather than an order to work through</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="39" customHeight="1" s="23">
+          <t>Weighted total = that cause's scores multiplied by the CTQ weights along the top and added up. With weights of 10, 9 and 7 (C11:E11) the closing-before-posting row totals 192 (H15). It is a ranking device, not a measurement — the auto-close row totals 192 as well (H22), and those two are one mechanism seen from both ends, so treat the top few as a set to investigate rather than an order to work through</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1" s="23">
       <c r="A21" s="56" t="inlineStr">
         <is>
-          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Read it with the totals beside it: rank 1 at 270 and rank 2 at 261 (H15, H16) is a photo finish, and a rank alone hides that</t>
+          <t>Rank = position by weighted total, 1 being highest. Ties are not broken, so two rows can share a rank. Always read it with the totals beside it: a rank on its own hides both a photo finish and an exact tie, and no amount of re-scoring separates two rows that scored the same</t>
         </is>
       </c>
     </row>
@@ -1068,8 +1077,19 @@
     <col width="40" customWidth="1" style="22" min="1" max="1"/>
     <col width="18" customWidth="1" style="22" min="2" max="2"/>
     <col width="13" customWidth="1" style="22" min="3" max="7"/>
+    <col width="13" customWidth="1" style="23" min="4" max="4"/>
+    <col width="13" customWidth="1" style="23" min="5" max="5"/>
+    <col width="13" customWidth="1" style="23" min="6" max="6"/>
+    <col width="13" customWidth="1" style="23" min="7" max="7"/>
     <col width="15" customWidth="1" style="22" min="8" max="8"/>
     <col width="8" customWidth="1" style="22" min="9" max="9"/>
+    <col width="13" customWidth="1" style="23" min="10" max="10"/>
+    <col width="13" customWidth="1" style="23" min="11" max="11"/>
+    <col width="13" customWidth="1" style="23" min="12" max="12"/>
+    <col width="13" customWidth="1" style="23" min="13" max="13"/>
+    <col width="13" customWidth="1" style="23" min="14" max="14"/>
+    <col width="13" customWidth="1" style="23" min="15" max="15"/>
+    <col width="13" customWidth="1" style="23" min="16" max="16"/>
     <col width="13" customWidth="1" style="23" min="17" max="17"/>
     <col width="13" customWidth="1" style="23" min="18" max="18"/>
     <col width="13" customWidth="1" style="23" min="19" max="19"/>
@@ -1155,29 +1175,21 @@
       </c>
       <c r="C10" s="37" t="inlineStr">
         <is>
-          <t>Issue solved first time</t>
+          <t>7-day reopen rate, in-scope billing adjustments (OD-BIL-004-ADJ)</t>
         </is>
       </c>
       <c r="D10" s="37" t="inlineStr">
         <is>
-          <t>Not asked to repeat myself</t>
+          <t>Share of in-scope adjustments confirmed posted before the case is closed</t>
         </is>
       </c>
       <c r="E10" s="37" t="inlineStr">
         <is>
-          <t>Resolved within SLA</t>
-        </is>
-      </c>
-      <c r="F10" s="37" t="inlineStr">
-        <is>
-          <t>Kept informed</t>
-        </is>
-      </c>
-      <c r="G10" s="37" t="inlineStr">
-        <is>
-          <t>Correct outcome</t>
-        </is>
-      </c>
+          <t>Share of contacts with a commitment date logged</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="n"/>
+      <c r="G10" s="37" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="23">
       <c r="B11" s="36" t="inlineStr">
@@ -1189,19 +1201,21 @@
         <v>10</v>
       </c>
       <c r="D11" s="38" t="n">
+        <v>9</v>
+      </c>
+      <c r="E11" s="38" t="n">
         <v>7</v>
       </c>
-      <c r="E11" s="38" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" s="38" t="n">
-        <v>5</v>
-      </c>
-      <c r="G11" s="38" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12"/>
+      <c r="F11" s="38" t="n"/>
+      <c r="G11" s="38" t="n"/>
+    </row>
+    <row r="12" ht="26" customHeight="1" s="23">
+      <c r="A12" s="58" t="inlineStr">
+        <is>
+          <t>Columns 4 and 5 are spare, and this example leaves them empty on purpose. The CTQ tree behind this project weights three requirements, so three are filled in. A fourth column with no tree row behind it has no weight anyone can defend, and the handle-time row the tree explicitly refuses to weight is the one most teams would have put there.</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="36" customHeight="1" s="23">
       <c r="A13" s="55" t="inlineStr">
         <is>
@@ -1295,17 +1309,13 @@
         <v>9</v>
       </c>
       <c r="D15" s="45" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="E15" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="F15" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="G15" s="45" t="n">
-        <v>9</v>
-      </c>
+      <c r="F15" s="45" t="n"/>
+      <c r="G15" s="45" t="n"/>
       <c r="H15" s="41">
         <f>IF(COUNT(C15:G15)=0,"",SUMPRODUCT(C15:G15,$C$11:$G$11))</f>
         <v/>
@@ -1344,20 +1354,16 @@
         </is>
       </c>
       <c r="C16" s="46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D16" s="46" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="E16" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="G16" s="46" t="n">
-        <v>6</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="F16" s="46" t="n"/>
+      <c r="G16" s="46" t="n"/>
       <c r="H16" s="41">
         <f>IF(COUNT(C16:G16)=0,"",SUMPRODUCT(C16:G16,$C$11:$G$11))</f>
         <v/>
@@ -1396,20 +1402,16 @@
         </is>
       </c>
       <c r="C17" s="46" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D17" s="46" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E17" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="F17" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="46" t="n">
-        <v>5</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F17" s="46" t="n"/>
+      <c r="G17" s="46" t="n"/>
       <c r="H17" s="41">
         <f>IF(COUNT(C17:G17)=0,"",SUMPRODUCT(C17:G17,$C$11:$G$11))</f>
         <v/>
@@ -1448,20 +1450,16 @@
         </is>
       </c>
       <c r="C18" s="46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" s="46" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E18" s="46" t="n">
-        <v>7</v>
-      </c>
-      <c r="F18" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="G18" s="46" t="n">
-        <v>4</v>
-      </c>
+      <c r="F18" s="46" t="n"/>
+      <c r="G18" s="46" t="n"/>
       <c r="H18" s="41">
         <f>IF(COUNT(C18:G18)=0,"",SUMPRODUCT(C18:G18,$C$11:$G$11))</f>
         <v/>
@@ -1500,20 +1498,16 @@
         </is>
       </c>
       <c r="C19" s="46" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="46" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E19" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="F19" s="46" t="n">
-        <v>9</v>
-      </c>
-      <c r="G19" s="46" t="n">
-        <v>3</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F19" s="46" t="n"/>
+      <c r="G19" s="46" t="n"/>
       <c r="H19" s="41">
         <f>IF(COUNT(C19:G19)=0,"",SUMPRODUCT(C19:G19,$C$11:$G$11))</f>
         <v/>
@@ -1555,17 +1549,13 @@
         <v>6</v>
       </c>
       <c r="D20" s="46" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E20" s="46" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="G20" s="46" t="n">
-        <v>8</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="F20" s="46" t="n"/>
+      <c r="G20" s="46" t="n"/>
       <c r="H20" s="41">
         <f>IF(COUNT(C20:G20)=0,"",SUMPRODUCT(C20:G20,$C$11:$G$11))</f>
         <v/>
@@ -1607,17 +1597,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E21" s="46" t="n">
-        <v>3</v>
-      </c>
-      <c r="F21" s="46" t="n">
-        <v>8</v>
-      </c>
-      <c r="G21" s="46" t="n">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F21" s="46" t="n"/>
+      <c r="G21" s="46" t="n"/>
       <c r="H21" s="41">
         <f>IF(COUNT(C21:G21)=0,"",SUMPRODUCT(C21:G21,$C$11:$G$11))</f>
         <v/>
@@ -1656,20 +1642,16 @@
         </is>
       </c>
       <c r="C22" s="46" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="46" t="n">
+        <v>9</v>
+      </c>
+      <c r="E22" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="46" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" s="46" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>7</v>
-      </c>
+      <c r="F22" s="46" t="n"/>
+      <c r="G22" s="46" t="n"/>
       <c r="H22" s="41">
         <f>IF(COUNT(C22:G22)=0,"",SUMPRODUCT(C22:G22,$C$11:$G$11))</f>
         <v/>
@@ -2103,14 +2085,9 @@
         <v/>
       </c>
       <c r="O34" s="48" t="n"/>
-      <c r="Q34" s="56" t="inlineStr">
-        <is>
-          <t>HOW TO READ IT.  Bars are the weighted totals, so height already accounts for which CTQ matters most. Look for a clear step down after the top few. Where the top bars are level — 270 against 261 here — the ranking is inside anyone's scoring noise, and you should treat them as one set to investigate rather than an order to work through.
-SO:  Take the top three into the fishbone and the FMEA together, not the top one on its own. 270 against 261 will not survive re-scoring by a different group.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1" s="23">
+      <c r="Q34" s="56" t="n"/>
+    </row>
+    <row r="35" ht="77" customHeight="1" s="23">
       <c r="A35" s="43" t="n"/>
       <c r="B35" s="43" t="n"/>
       <c r="C35" s="43" t="n"/>
@@ -2143,8 +2120,9 @@
         <v/>
       </c>
       <c r="O35" s="48" t="n"/>
-    </row>
-    <row r="36">
+      <c r="Q35" s="56" t="n"/>
+    </row>
+    <row r="36" ht="88" customHeight="1" s="23">
       <c r="J36" s="48" t="n"/>
       <c r="K36" s="50">
         <f>IF(H36="","",RANK(H36,$H$15:$H$36,0)+COUNTIF($H$15:H36,H36)-1)</f>
@@ -2162,6 +2140,12 @@
         <v/>
       </c>
       <c r="O36" s="48" t="n"/>
+      <c r="Q36" s="56" t="inlineStr">
+        <is>
+          <t>HOW TO READ IT.  Bars are the weighted totals, so height already accounts for which CTQ matters most. Look for a clear step down after the top few. Where the top bars are level — two rows at 192 here, and two more at 148 — the matrix has not ranked them and cannot, so treat each level set as one thing to investigate rather than an order to work through.
+SO:  Take the top four into the fishbone and the FMEA together, not the top one on its own — the ties put four rows in the top two ranks. None of it survives re-scoring by a different group, which is the point: this orders your investigation, not your evidence.</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="25.5" customHeight="1" s="23">
       <c r="A37" s="44" t="inlineStr">
@@ -2171,7 +2155,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="13">
     <mergeCell ref="Q34:Y34"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="A2:I2"/>
@@ -2180,8 +2164,11 @@
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A12:Y12"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A4:F4"/>
+    <mergeCell ref="Q36:Y36"/>
+    <mergeCell ref="Q35:Y35"/>
   </mergeCells>
   <conditionalFormatting sqref="H15:H35">
     <cfRule type="colorScale" priority="2">

--- a/templates/11-cause-effect-xy-matrix.xlsx
+++ b/templates/11-cause-effect-xy-matrix.xlsx
@@ -2164,10 +2164,10 @@
     <mergeCell ref="A13:I13"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:Y12"/>
     <mergeCell ref="A9:I9"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="Q36:Y36"/>
+    <mergeCell ref="A12:Y12"/>
     <mergeCell ref="Q35:Y35"/>
   </mergeCells>
   <conditionalFormatting sqref="H15:H35">
